--- a/光伏配储项目/电价数据/2026/铁山站.xlsx
+++ b/光伏配储项目/电价数据/2026/铁山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34288</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8617100000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07668999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.01471</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.0873</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17448</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25573</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24503</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.86413</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.51615</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.62163</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6033999999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.77691</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.26004</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.71183</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.69368</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.97777</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53925</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.32073</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.42501</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.18954</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.26615</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.4431</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.57497</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.50334</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7748200000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.83497</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.30967</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.2353</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8590399999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.81657</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.49081</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.44556</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.74505</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9331799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.99614</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50685</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52547</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51559</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51547</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49627</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.47603</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.48858</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6762699999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.64135</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8337899999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.15855</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.52039</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.66223</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.93779</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6153</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.78201</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.83435</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.26206</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.71613</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.23026</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9075800000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.33317</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.2149</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.40221</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.12266</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.19954</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6991799999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.06823</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9428099999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9521499999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.17267</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9434900000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45311</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90132</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9337000000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45225</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44657</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33518</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51719</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43492</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45151</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48195</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.14209</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.18227</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.8317599999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.6789400000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.66638</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.8490700000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.84276</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8480599999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.85172</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8660099999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8758899999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.01102</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.59246</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80383</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8081799999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.68291</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7138</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.52425</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.80111</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45697</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51487</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52399</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6415</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.63912</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6552100000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28707</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62375</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70094</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47016</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.63117</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.77147</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7690900000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.89147</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.46232</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6492</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.53118</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61774</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7938</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9069299999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.73114</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.61674</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.56584</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.70927</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34262</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.54006</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46497</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49286</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.62762</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.74182</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.61072</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.52774</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48744</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6446900000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50387</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.67411</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.49889</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66162</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.53595</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.50512</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46258</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.43947</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32536</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02259</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26253</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24757</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.07503</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31546</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.23803</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22424</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18413</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16729</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24396</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20861</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18595</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16642</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24448</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19386</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10138</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04272</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009820000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20583</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04908</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19931</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00831</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05998</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05818</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31474</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33722</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46114</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78579</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702799999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57129</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45377</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60642</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89411</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46775</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.58977</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8361900000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.58873</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.44098</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25927</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27875</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32196</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95925</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.49127</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.50744</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20557</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.19599</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43086</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.29745</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.21956</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8312</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.51798</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14681</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8057300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64034</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.21165</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.21206</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43805</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49223</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44734</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46651</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.15908</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25706</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02389</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25814</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.44577</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.57577</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.25869</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.15601</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17973</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17554</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17705</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23251</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.14208</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.17733</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.17663</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.19469</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.18278</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.17285</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.14101</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26587</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24403</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27773</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.45506</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.47855</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30349</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.28174</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43842</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7466699999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.53099</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48542</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5415099999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.45728</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6140399999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7802100000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.46349</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6017</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.48052</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.46941</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.67945</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.49243</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50805</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71521</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47959</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22141</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.1963</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19006</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18264</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18435</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18179</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14365</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18153</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18731</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.21033</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19357</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14783</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20661</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23119</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26584</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25182</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20411</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.15715</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22764</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31795</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.03863</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6625800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.57357</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19524</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29389</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.4727</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49229</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.70121</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65419</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7061499999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.86478</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5269299999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31154</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44632</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41878</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.47154</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5129900000000001</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.56041</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57217</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6747799999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.87725</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.54753</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7950900000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62812</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6408400000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30725</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.02415</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.50736</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21465</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.21602</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21187</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23428</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.22265</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17227</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17594</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20619</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.18038</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.22114</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21021</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.15568</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.02674</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25551</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.02867</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.02794</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.15593</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.04036</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19115</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15471</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.02771</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14584</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15012</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18715</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15047</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15304</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.02778</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15561</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.02785</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16592</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17357</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13872</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26395</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.55691</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.23297</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00206</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24353</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26111</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20987</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22985</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21055</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25756</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24593</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.16447</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.17159</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15385</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15467</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22733</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22307</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28516</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17591</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17307</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.03177</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19608</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21791</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.04407</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.02951</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.02952</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.02974</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.02974</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.02961</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19066</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.04415</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.02974</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.02973</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16832</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02898</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24289</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00865</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14904</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01509</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03715</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01669</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03583</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02897</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27902</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26481</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.01626</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15436</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15855</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15606</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15229</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.02632</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.02537</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.02382</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18184</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22672</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85653</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8624400000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08921999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.02485</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24552</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5521699999999999</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00259</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00185</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06939000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.73403</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5615800000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.87863</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.03977</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.65047</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.87774</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8759600000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.88081</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.99033</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30393</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48709</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26226</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25695</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17976</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25401</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24822</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24185</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20809</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24377</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19402</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18974</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15175</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15432</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17108</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22285</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23173</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24741</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28721</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49031</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.16969</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8777699999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.89174</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5652699999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.7375499999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.92667</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.62098</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31326</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.56148</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58002</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.29975</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.92988</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.61779</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.83084</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51828</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6504500000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57192</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.80043</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.73305</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.23075</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.77628</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.63449</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31789</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5435800000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19868</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51192</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.52459</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42218</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.47544</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.49429</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.62386</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5134500000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32162</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.76701</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47991</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.49356</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43587</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.45613</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.45825</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33537</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19872</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14711</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04822</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12197</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22659</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26016</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14302</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14579</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18716</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22691</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16871</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20294</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.17195</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.50541</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.44578</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43654</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3666</v>
       </c>
     </row>
   </sheetData>
